--- a/tests/fixtures/expected/Test_Range_Multiline.xlsx
+++ b/tests/fixtures/expected/Test_Range_Multiline.xlsx
@@ -367,10 +367,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="4">
-    <numFmt numFmtId="178" formatCode="#\ ##0"/>
     <numFmt numFmtId="177" formatCode="#\ ##0.0000"/>
     <numFmt numFmtId="176" formatCode="#\ ##0.00"/>
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="178" formatCode="#\ ##0"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
